--- a/framework/data/excel/cart_hybrid.xlsx
+++ b/framework/data/excel/cart_hybrid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DA4\DA4_hybrid_selenium_framework\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50A79D3-0FD5-47DB-BC42-CFA8ED778A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347E2CC4-6C05-4734-A909-EE24AC5CD66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_step" sheetId="1" r:id="rId1"/>
@@ -514,7 +514,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -534,6 +534,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE9EFF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -564,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -587,6 +599,20 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2251,83 +2277,83 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8">
         <v>-1</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="7" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="6" t="s">
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="12" t="s">
         <v>139</v>
       </c>
     </row>

--- a/framework/data/excel/cart_hybrid.xlsx
+++ b/framework/data/excel/cart_hybrid.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DA4\DA4_hybrid_selenium_framework\framework\data\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347E2CC4-6C05-4734-A909-EE24AC5CD66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D29622-2AE4-4A23-B403-80C0CCAE1588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="test_step" sheetId="1" r:id="rId1"/>
+    <sheet name="test_steps" sheetId="1" r:id="rId1"/>
     <sheet name="test_case" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -916,9 +916,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.5546875" customWidth="1"/>
+    <col min="1" max="1" width="39.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
@@ -926,7 +926,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,7 +946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -962,7 +962,7 @@
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -980,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1014,7 +1014,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -1082,7 +1082,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -1114,7 +1114,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -1198,7 +1198,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>37</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>37</v>
       </c>
@@ -1304,7 +1304,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>37</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>44</v>
       </c>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>44</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>49</v>
       </c>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>49</v>
       </c>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>49</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>55</v>
       </c>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>55</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>55</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>55</v>
       </c>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>55</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>55</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>55</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>68</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>68</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="F39" s="5"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>68</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>68</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>68</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>68</v>
       </c>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>68</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>75</v>
       </c>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F45" s="5"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>75</v>
       </c>
@@ -1726,7 +1726,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>75</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>75</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>82</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>82</v>
       </c>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>82</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>82</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>82</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>82</v>
       </c>
@@ -1870,7 +1870,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>82</v>
       </c>
@@ -1896,10 +1896,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="37.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
@@ -1919,7 +1919,7 @@
     <col min="24" max="24" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>95</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>118</v>
       </c>
@@ -2027,7 +2027,7 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
     </row>
-    <row r="3" spans="1:24" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>123</v>
       </c>
@@ -2097,7 +2097,7 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>130</v>
       </c>
@@ -2135,7 +2135,7 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
     </row>
-    <row r="6" spans="1:24" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>131</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>149</v>
       </c>
@@ -2207,7 +2207,7 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>140</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>144</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>147</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>148</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>119</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>126</v>
       </c>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="X13" s="4"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>150</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>151</v>
       </c>
